--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108664</v>
+        <v>108676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108676</v>
+        <v>108677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108677</v>
+        <v>108682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108682</v>
+        <v>108686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108686</v>
+        <v>108688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108688</v>
+        <v>108698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108698</v>
+        <v>108702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108702</v>
+        <v>108705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108705</v>
+        <v>108706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 68261-2020 artfynd.xlsx
+++ b/artfynd/A 68261-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129676674</v>
       </c>
       <c r="B2" t="n">
-        <v>108706</v>
+        <v>108723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
